--- a/MEV/SCHEDA_2026-1/B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx
+++ b/MEV/SCHEDA_2026-1/B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx
@@ -50,7 +50,7 @@
     <definedName name="UserNames" localSheetId="3">#REF!</definedName>
     <definedName name="UserNames">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1136,9 +1136,6 @@
     </r>
   </si>
   <si>
-    <t>Verificare che la form sia impaginata e presenti 20 risultati per pagina ordinata per data fine decrescente, per ciascuna riga siano riportati: Anno e Numero procedimento SIUS, Stato Procedimento, Cognome e Nome soggetto, Luogo e Data nascita, Posizione Giuridica, Contenuto, Data inizio pena, Data Fine Pena, giorni residui alla scadenza dalla data odierna, Fine pena virtuale, giorni residui alla scadenza, Anno e Numero procedimento SIEP</t>
-  </si>
-  <si>
     <t>Verifica: Verificare nel sottosistema SIUS la funzione Ricerca Fine Pena Procedimenti Pendenti per data fine pena reale</t>
   </si>
   <si>
@@ -1182,9 +1179,6 @@
     <t>Per alcuni dei procedimenti SIEP estratti nel precedente Test, lato SIEP bisogna calcolare la data fine pena virtuale</t>
   </si>
   <si>
-    <t>Verificare che la form sia impaginata e presenti 20 risultati per pagina ordinata per data fine vrtuale decrescente, per ciascuna riga siano riportati: Anno e Numero procedimento SIUS, Stato Procedimento, Cognome e Nome soggetto, Luogo e Data nascita, Posizione Giuridica, Contenuto, Data inizio pena, Data Fine Pena, giorni residui alla scadenza dalla data odierna, Fine pena virtuale, giorni residui alla scadenza, Anno e Numero procedimento SIEP</t>
-  </si>
-  <si>
     <t>PAR.3.2-048-04</t>
   </si>
   <si>
@@ -1257,6 +1251,12 @@
       </rPr>
       <t>con il Dettaglio di tutti i dati coinvolti nel calcolo e i risultati dello stesso</t>
     </r>
+  </si>
+  <si>
+    <t>Verificare che la form sia impaginata e presenti 20 risultati per pagina ordinata per data fine decrescente, per ciascuna riga siano riportati: Anno e Numero procedimento SIUS, Cognome e Nome soggetto, Luogo e Data nascita, Posizione Giuridica, Contenuto, Data inizio pena, Data Fine Pena, giorni residui alla scadenza dalla data odierna, Fine pena virtuale, giorni residui alla scadenza, Anno e Numero procedimento SIEP</t>
+  </si>
+  <si>
+    <t>Verificare che la form sia impaginata e presenti 20 risultati per pagina ordinata per data fine vrtuale decrescente, per ciascuna riga siano riportati: Anno e Numero procedimento SIUS, Cognome e Nome soggetto, Luogo e Data nascita, Posizione Giuridica, Contenuto, Data inizio pena, Data Fine Pena, giorni residui alla scadenza dalla data odierna, Fine pena virtuale, giorni residui alla scadenza, Anno e Numero procedimento SIEP</t>
   </si>
 </sst>
 </file>
@@ -2555,6 +2555,120 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="16" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="16" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2580,18 +2694,54 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2601,30 +2751,6 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2661,6 +2787,69 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2685,195 +2874,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="16" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="15" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="16" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2949,7 +2949,7 @@
         <xdr:cNvPr id="2" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BE6E059E-EBBA-4582-A85D-A320D8B7368E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE6E059E-EBBA-4582-A85D-A320D8B7368E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3023,7 +3023,7 @@
         <xdr:cNvPr id="3" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A433206B-F0DA-431B-8027-14A3EAB8CDD7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A433206B-F0DA-431B-8027-14A3EAB8CDD7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3097,7 +3097,7 @@
         <xdr:cNvPr id="4" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A98800D-9369-472C-98BF-839009E35F03}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A98800D-9369-472C-98BF-839009E35F03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3171,7 +3171,7 @@
         <xdr:cNvPr id="13" name="Picture 4" descr="Text&#10;&#10;Description automatically generated">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000D000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3232,7 +3232,7 @@
         <xdr:cNvPr id="14" name="Picture 6" descr="Graphical user interface, text&#10;&#10;Description automatically generated with medium confidence">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000E000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3293,7 +3293,7 @@
         <xdr:cNvPr id="15" name="Picture 5" descr="A picture containing text&#10;&#10;Description automatically generated">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00000F000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3354,7 +3354,7 @@
         <xdr:cNvPr id="19" name="Immagine 18" descr="A blue and white circular logo&#10;&#10;Description automatically generated">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000013000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3774,7 +3774,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4107,54 +4107,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77"/>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
+      <c r="A1" s="115"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
     </row>
     <row r="2" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
+      <c r="A3" s="119"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="N3" s="118"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
@@ -4163,18 +4163,18 @@
       <c r="B4" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
@@ -4183,18 +4183,18 @@
       <c r="B5" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
@@ -4203,18 +4203,18 @@
       <c r="B6" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
@@ -4223,18 +4223,18 @@
       <c r="B7" s="37">
         <v>46052</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
@@ -4243,18 +4243,18 @@
       <c r="B8" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="118"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
@@ -4263,70 +4263,70 @@
       <c r="B9" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="80"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
     </row>
     <row r="10" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="80"/>
-      <c r="M10" s="80"/>
-      <c r="N10" s="80"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="118"/>
     </row>
     <row r="11" spans="1:14" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="80"/>
-      <c r="N11" s="80"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="118"/>
+      <c r="L11" s="118"/>
+      <c r="M11" s="118"/>
+      <c r="N11" s="118"/>
     </row>
     <row r="12" spans="1:14" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="77"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
-      <c r="L12" s="80"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="80"/>
+      <c r="A12" s="115"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
     </row>
     <row r="61" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -4367,68 +4367,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="82" t="str">
+      <c r="B1" s="121"/>
+      <c r="C1" s="120" t="str">
         <f>Copertina!B8</f>
         <v>MEV 2026_1 Scheda Intervento Evolutive di SIES v1.0</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="82" t="str">
+      <c r="B2" s="121"/>
+      <c r="C2" s="120" t="str">
         <f>Copertina!B4</f>
         <v>B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="175" t="s">
+      <c r="B3" s="108" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="176" t="s">
+      <c r="D3" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="176" t="s">
+      <c r="E3" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="177" t="s">
+      <c r="F3" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="178" t="s">
+      <c r="G3" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="179" t="s">
+      <c r="H3" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="180" t="s">
+      <c r="I3" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="177" t="s">
+      <c r="J3" s="110" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       <c r="D4" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="163" t="s">
+      <c r="E4" s="96" t="s">
         <v>94</v>
       </c>
       <c r="F4" s="50" t="str">
@@ -4465,227 +4465,227 @@
       <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="166" t="s">
+      <c r="D5" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="167" t="s">
+      <c r="E5" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="166" t="str">
+      <c r="F5" s="99" t="str">
         <f t="shared" ref="F5" si="1">CONCATENATE("TF0",MID(B5,LEN(B5)-1,2),".",D5)</f>
         <v>TF001.UC02</v>
       </c>
-      <c r="G5" s="168" t="s">
+      <c r="G5" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="166">
+      <c r="H5" s="99">
         <v>3</v>
       </c>
-      <c r="I5" s="166" t="s">
+      <c r="I5" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="169"/>
+      <c r="J5" s="102"/>
       <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="164" t="s">
+      <c r="A6" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="165" t="s">
+      <c r="B6" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="165" t="s">
+      <c r="C6" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="166" t="s">
+      <c r="D6" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="167" t="s">
+      <c r="E6" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="166" t="str">
+      <c r="F6" s="99" t="str">
         <f t="shared" ref="F6" si="2">CONCATENATE("TF0",MID(B6,LEN(B6)-1,2),".",D6)</f>
         <v>TF001.UC03</v>
       </c>
-      <c r="G6" s="168" t="s">
+      <c r="G6" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="166">
+      <c r="H6" s="99">
         <v>3</v>
       </c>
-      <c r="I6" s="166" t="s">
+      <c r="I6" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="169"/>
+      <c r="J6" s="102"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="164" t="s">
+      <c r="A7" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="165" t="s">
+      <c r="B7" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="166" t="s">
+      <c r="D7" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="167" t="s">
+      <c r="E7" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="166" t="str">
+      <c r="F7" s="99" t="str">
         <f t="shared" ref="F7" si="3">CONCATENATE("TF0",MID(B7,LEN(B7)-1,2),".",D7)</f>
         <v>TF001.UC04</v>
       </c>
-      <c r="G7" s="168" t="s">
+      <c r="G7" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="166">
+      <c r="H7" s="99">
         <v>3</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="169"/>
+      <c r="J7" s="102"/>
       <c r="K7" s="55"/>
     </row>
     <row r="8" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="164" t="s">
+      <c r="A8" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="165" t="s">
+      <c r="B8" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="165" t="s">
+      <c r="C8" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="166" t="s">
+      <c r="D8" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="167" t="s">
+      <c r="E8" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="166" t="str">
+      <c r="F8" s="99" t="str">
         <f t="shared" ref="F8" si="4">CONCATENATE("TF0",MID(B8,LEN(B8)-1,2),".",D8)</f>
         <v>TF002.UC01</v>
       </c>
-      <c r="G8" s="168" t="s">
+      <c r="G8" s="101" t="s">
         <v>128</v>
       </c>
-      <c r="H8" s="166">
+      <c r="H8" s="99">
         <v>3</v>
       </c>
-      <c r="I8" s="166" t="s">
+      <c r="I8" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="169"/>
+      <c r="J8" s="102"/>
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="164" t="s">
+      <c r="A9" s="97" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="98" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="98" t="s">
         <v>145</v>
       </c>
-      <c r="D9" s="166" t="s">
+      <c r="D9" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="167" t="s">
+      <c r="E9" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="166" t="str">
+      <c r="F9" s="99" t="str">
         <f t="shared" ref="F9" si="5">CONCATENATE("TF0",MID(B9,LEN(B9)-1,2),".",D9)</f>
         <v>TF003.UC01</v>
       </c>
-      <c r="G9" s="168" t="s">
-        <v>156</v>
-      </c>
-      <c r="H9" s="166">
+      <c r="G9" s="101" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" s="99">
         <v>3</v>
       </c>
-      <c r="I9" s="166" t="s">
+      <c r="I9" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="169"/>
+      <c r="J9" s="102"/>
       <c r="K9" s="55"/>
     </row>
     <row r="10" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="164" t="s">
+      <c r="A10" s="97" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="165" t="s">
+      <c r="B10" s="98" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="165" t="s">
+      <c r="C10" s="98" t="s">
         <v>145</v>
       </c>
-      <c r="D10" s="166" t="s">
+      <c r="D10" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="167" t="s">
+      <c r="E10" s="100" t="s">
         <v>146</v>
       </c>
-      <c r="F10" s="166" t="str">
+      <c r="F10" s="99" t="str">
         <f t="shared" ref="F10:F11" si="6">CONCATENATE("TF0",MID(B10,LEN(B10)-1,2),".",D10)</f>
         <v>TF003.UC02</v>
       </c>
-      <c r="G10" s="168" t="s">
-        <v>157</v>
-      </c>
-      <c r="H10" s="166">
+      <c r="G10" s="101" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="99">
         <v>3</v>
       </c>
-      <c r="I10" s="166" t="s">
+      <c r="I10" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="169"/>
+      <c r="J10" s="102"/>
       <c r="K10" s="55"/>
     </row>
     <row r="11" spans="1:11" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="170" t="s">
+      <c r="A11" s="103" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="171" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="171" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="172" t="s">
+      <c r="B11" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="173" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="172" t="str">
+      <c r="E11" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="105" t="str">
         <f t="shared" si="6"/>
         <v>TF004.UC01</v>
       </c>
-      <c r="G11" s="173" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="172">
+      <c r="G11" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" s="105">
         <v>3</v>
       </c>
-      <c r="I11" s="172" t="s">
+      <c r="I11" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="174"/>
+      <c r="J11" s="107"/>
       <c r="K11" s="55"/>
     </row>
   </sheetData>
@@ -4721,73 +4721,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="82" t="str">
+      <c r="B1" s="137"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="120" t="str">
         <f>Copertina!B8</f>
         <v>MEV 2026_1 Scheda Intervento Evolutive di SIES v1.0</v>
       </c>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="82" t="str">
+      <c r="B2" s="138"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="120" t="str">
         <f>Copertina!B4</f>
         <v>B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90" t="s">
+      <c r="E3" s="140"/>
+      <c r="F3" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="90"/>
+      <c r="G3" s="140"/>
     </row>
     <row r="4" spans="1:7" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="74" t="str">
         <f>TabellaTest!F4</f>
         <v>TF001.UC01</v>
       </c>
-      <c r="B4" s="92" t="str">
+      <c r="B4" s="130" t="str">
         <f>TabellaTest!C4</f>
         <v>PAR. 2.1-048-01</v>
       </c>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91" t="str">
+      <c r="C4" s="131"/>
+      <c r="D4" s="131" t="str">
         <f>TabellaTest!E4</f>
         <v>Visualizzazione Data Fine Pena Virtuale su Dettaglio Procedimento</v>
       </c>
-      <c r="E4" s="87"/>
-      <c r="F4" s="91" t="str">
+      <c r="E4" s="132"/>
+      <c r="F4" s="131" t="str">
         <f>TabellaTest!G4</f>
         <v>Verifica: Verificare nel sottosistema SIEP la funzione Storico Calcoli Validati su Calcolo Pena DL 92/2024 in caso di assenza storico</v>
       </c>
-      <c r="G4" s="87"/>
+      <c r="G4" s="132"/>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
+      <c r="A5" s="133"/>
       <c r="B5" s="58" t="s">
         <v>31</v>
       </c>
@@ -4808,8 +4808,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85"/>
-      <c r="B6" s="139" t="s">
+      <c r="A6" s="134"/>
+      <c r="B6" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="39" t="s">
@@ -4825,8 +4825,8 @@
       <c r="G6" s="41"/>
     </row>
     <row r="7" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="85"/>
-      <c r="B7" s="139" t="s">
+      <c r="A7" s="134"/>
+      <c r="B7" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -4842,8 +4842,8 @@
       <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
-      <c r="B8" s="140">
+      <c r="A8" s="134"/>
+      <c r="B8" s="77">
         <v>1</v>
       </c>
       <c r="C8" s="42" t="s">
@@ -4859,8 +4859,8 @@
       <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="85"/>
-      <c r="B9" s="141" t="s">
+      <c r="A9" s="134"/>
+      <c r="B9" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="72" t="s">
@@ -4874,8 +4874,8 @@
       <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="85"/>
-      <c r="B10" s="142">
+      <c r="A10" s="134"/>
+      <c r="B10" s="79">
         <v>2</v>
       </c>
       <c r="C10" s="45" t="s">
@@ -4891,11 +4891,11 @@
       <c r="G10" s="41"/>
     </row>
     <row r="11" spans="1:7" s="29" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="85"/>
-      <c r="B11" s="143" t="s">
+      <c r="A11" s="134"/>
+      <c r="B11" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D11" s="75" t="s">
@@ -4910,24 +4910,24 @@
         <f>TabellaTest!F5</f>
         <v>TF001.UC02</v>
       </c>
-      <c r="B12" s="92" t="str">
+      <c r="B12" s="130" t="str">
         <f>TabellaTest!C5</f>
         <v>PAR. 2.1-048-01</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91" t="str">
+      <c r="C12" s="131"/>
+      <c r="D12" s="131" t="str">
         <f>TabellaTest!E5</f>
         <v>Visualizzazione Data Fine Pena Virtuale su Dettaglio Procedimento</v>
       </c>
-      <c r="E12" s="87"/>
-      <c r="F12" s="91" t="str">
+      <c r="E12" s="132"/>
+      <c r="F12" s="131" t="str">
         <f>TabellaTest!G5</f>
         <v xml:space="preserve">Verifica: Verificare nel sottosistema SIEP la funzione Valida su Calcolo Pena DL 92/2024 </v>
       </c>
-      <c r="G12" s="87"/>
+      <c r="G12" s="132"/>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
+      <c r="A13" s="133"/>
       <c r="B13" s="58" t="s">
         <v>31</v>
       </c>
@@ -4948,7 +4948,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="85"/>
+      <c r="A14" s="134"/>
       <c r="B14" s="60" t="s">
         <v>36</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="G14" s="41"/>
     </row>
     <row r="15" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="85"/>
+      <c r="A15" s="134"/>
       <c r="B15" s="60" t="s">
         <v>36</v>
       </c>
@@ -4982,7 +4982,7 @@
       <c r="G15" s="41"/>
     </row>
     <row r="16" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
+      <c r="A16" s="134"/>
       <c r="B16" s="61">
         <v>1</v>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="G16" s="41"/>
     </row>
     <row r="17" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
+      <c r="A17" s="134"/>
       <c r="B17" s="62">
         <v>2</v>
       </c>
@@ -5016,7 +5016,7 @@
       <c r="G17" s="41"/>
     </row>
     <row r="18" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="85"/>
+      <c r="A18" s="134"/>
       <c r="B18" s="63">
         <v>3</v>
       </c>
@@ -5033,7 +5033,7 @@
       <c r="G18" s="41"/>
     </row>
     <row r="19" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="85"/>
+      <c r="A19" s="134"/>
       <c r="B19" s="63">
         <v>4</v>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="G19" s="41"/>
     </row>
     <row r="20" spans="1:7" s="29" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="85"/>
+      <c r="A20" s="134"/>
       <c r="B20" s="64" t="s">
         <v>77</v>
       </c>
@@ -5069,24 +5069,24 @@
         <f>TabellaTest!F6</f>
         <v>TF001.UC03</v>
       </c>
-      <c r="B21" s="92" t="str">
+      <c r="B21" s="130" t="str">
         <f>TabellaTest!F6</f>
         <v>TF001.UC03</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91" t="str">
+      <c r="C21" s="131"/>
+      <c r="D21" s="131" t="str">
         <f>TabellaTest!E6</f>
         <v>Visualizzazione Data Fine Pena Virtuale su Dettaglio Procedimento</v>
       </c>
-      <c r="E21" s="87"/>
-      <c r="F21" s="91" t="str">
+      <c r="E21" s="132"/>
+      <c r="F21" s="131" t="str">
         <f>TabellaTest!G6</f>
         <v xml:space="preserve">Verifica: Verificare nel sottosistema SIEP la funzione Storico Calcoli Validati su Calcolo Pena DL 92/2024 </v>
       </c>
-      <c r="G21" s="87"/>
+      <c r="G21" s="132"/>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="133"/>
       <c r="B22" s="58" t="s">
         <v>31</v>
       </c>
@@ -5107,8 +5107,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="139" t="s">
+      <c r="A23" s="134"/>
+      <c r="B23" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="39" t="s">
@@ -5122,8 +5122,8 @@
       <c r="G23" s="41"/>
     </row>
     <row r="24" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
-      <c r="B24" s="142">
+      <c r="A24" s="134"/>
+      <c r="B24" s="79">
         <v>1</v>
       </c>
       <c r="C24" s="45" t="s">
@@ -5139,8 +5139,8 @@
       <c r="G24" s="41"/>
     </row>
     <row r="25" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="141" t="s">
+      <c r="A25" s="134"/>
+      <c r="B25" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="72" t="s">
@@ -5154,8 +5154,8 @@
       <c r="G25" s="41"/>
     </row>
     <row r="26" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="145">
+      <c r="A26" s="134"/>
+      <c r="B26" s="82">
         <v>3</v>
       </c>
       <c r="C26" s="45" t="s">
@@ -5171,8 +5171,8 @@
       <c r="G26" s="41"/>
     </row>
     <row r="27" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
-      <c r="B27" s="141" t="s">
+      <c r="A27" s="134"/>
+      <c r="B27" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C27" s="72" t="s">
@@ -5186,17 +5186,17 @@
       <c r="G27" s="41"/>
     </row>
     <row r="28" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
-      <c r="B28" s="146">
+      <c r="A28" s="134"/>
+      <c r="B28" s="83">
         <v>4</v>
       </c>
-      <c r="C28" s="147" t="s">
+      <c r="C28" s="84" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="148"/>
+      <c r="E28" s="85"/>
       <c r="F28" s="75" t="s">
         <v>116</v>
       </c>
@@ -5207,24 +5207,24 @@
         <f>TabellaTest!F7</f>
         <v>TF001.UC04</v>
       </c>
-      <c r="B29" s="92" t="str">
+      <c r="B29" s="130" t="str">
         <f>TabellaTest!F7</f>
         <v>TF001.UC04</v>
       </c>
-      <c r="C29" s="91"/>
-      <c r="D29" s="91" t="str">
+      <c r="C29" s="131"/>
+      <c r="D29" s="131" t="str">
         <f>TabellaTest!E7</f>
         <v>Visualizzazione Data Fine Pena Virtuale su Dettaglio Procedimento</v>
       </c>
-      <c r="E29" s="87"/>
-      <c r="F29" s="91" t="str">
+      <c r="E29" s="132"/>
+      <c r="F29" s="131" t="str">
         <f>TabellaTest!G7</f>
         <v>Verifica: Verificare nel sottosistema SIEP la funzione Dettaglio Procedimento</v>
       </c>
-      <c r="G29" s="87"/>
+      <c r="G29" s="132"/>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="133"/>
       <c r="B30" s="58" t="s">
         <v>31</v>
       </c>
@@ -5245,8 +5245,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="139" t="s">
+      <c r="A31" s="134"/>
+      <c r="B31" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C31" s="39" t="s">
@@ -5262,8 +5262,8 @@
       <c r="G31" s="41"/>
     </row>
     <row r="32" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="139" t="s">
+      <c r="A32" s="134"/>
+      <c r="B32" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C32" s="39" t="s">
@@ -5279,8 +5279,8 @@
       <c r="G32" s="41"/>
     </row>
     <row r="33" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="142">
+      <c r="A33" s="134"/>
+      <c r="B33" s="79">
         <v>1</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -5296,8 +5296,8 @@
       <c r="G33" s="41"/>
     </row>
     <row r="34" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="141" t="s">
+      <c r="A34" s="134"/>
+      <c r="B34" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C34" s="72" t="s">
@@ -5311,8 +5311,8 @@
       <c r="G34" s="41"/>
     </row>
     <row r="35" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="85"/>
-      <c r="B35" s="145">
+      <c r="A35" s="134"/>
+      <c r="B35" s="82">
         <v>2</v>
       </c>
       <c r="C35" s="45" t="s">
@@ -5328,8 +5328,8 @@
       <c r="G35" s="41"/>
     </row>
     <row r="36" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="141" t="s">
+      <c r="A36" s="134"/>
+      <c r="B36" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="72" t="s">
@@ -5343,17 +5343,17 @@
       <c r="G36" s="41"/>
     </row>
     <row r="37" spans="1:7" s="29" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="146">
+      <c r="A37" s="134"/>
+      <c r="B37" s="83">
         <v>3</v>
       </c>
-      <c r="C37" s="147" t="s">
+      <c r="C37" s="84" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="75" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="148"/>
+      <c r="E37" s="85"/>
       <c r="F37" s="47" t="s">
         <v>123</v>
       </c>
@@ -5364,24 +5364,24 @@
         <f>TabellaTest!F8</f>
         <v>TF002.UC01</v>
       </c>
-      <c r="B38" s="92" t="str">
+      <c r="B38" s="130" t="str">
         <f>TabellaTest!F8</f>
         <v>TF002.UC01</v>
       </c>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91" t="str">
+      <c r="C38" s="131"/>
+      <c r="D38" s="131" t="str">
         <f>TabellaTest!E8</f>
         <v>Visualizzazione Scadenzario Fine Pena</v>
       </c>
-      <c r="E38" s="87"/>
-      <c r="F38" s="91" t="str">
+      <c r="E38" s="132"/>
+      <c r="F38" s="131" t="str">
         <f>TabellaTest!G8</f>
         <v>Verifica: Verificare nel sottosistema SIEP la funzione Scadenzario Fine Pena</v>
       </c>
-      <c r="G38" s="87"/>
+      <c r="G38" s="132"/>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="84"/>
+      <c r="A39" s="133"/>
       <c r="B39" s="58" t="s">
         <v>31</v>
       </c>
@@ -5402,8 +5402,8 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="139" t="s">
+      <c r="A40" s="134"/>
+      <c r="B40" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="39" t="s">
@@ -5419,8 +5419,8 @@
       <c r="G40" s="41"/>
     </row>
     <row r="41" spans="1:7" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="139" t="s">
+      <c r="A41" s="134"/>
+      <c r="B41" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C41" s="39" t="s">
@@ -5434,8 +5434,8 @@
       <c r="G41" s="41"/>
     </row>
     <row r="42" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="140">
+      <c r="A42" s="134"/>
+      <c r="B42" s="77">
         <v>1</v>
       </c>
       <c r="C42" s="42" t="s">
@@ -5451,8 +5451,8 @@
       <c r="G42" s="41"/>
     </row>
     <row r="43" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="142">
+      <c r="A43" s="134"/>
+      <c r="B43" s="79">
         <v>2</v>
       </c>
       <c r="C43" s="45" t="s">
@@ -5468,8 +5468,8 @@
       <c r="G43" s="41"/>
     </row>
     <row r="44" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="141" t="s">
+      <c r="A44" s="134"/>
+      <c r="B44" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C44" s="72" t="s">
@@ -5483,8 +5483,8 @@
       <c r="G44" s="41"/>
     </row>
     <row r="45" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="85"/>
-      <c r="B45" s="139" t="s">
+      <c r="A45" s="134"/>
+      <c r="B45" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C45" s="39" t="s">
@@ -5498,8 +5498,8 @@
       <c r="G45" s="41"/>
     </row>
     <row r="46" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="85"/>
-      <c r="B46" s="149" t="s">
+      <c r="A46" s="134"/>
+      <c r="B46" s="86" t="s">
         <v>137</v>
       </c>
       <c r="C46" s="69" t="s">
@@ -5513,11 +5513,11 @@
       <c r="G46" s="41"/>
     </row>
     <row r="47" spans="1:7" s="29" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="143" t="s">
+      <c r="A47" s="134"/>
+      <c r="B47" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D47" s="75" t="s">
@@ -5532,62 +5532,62 @@
         <f>TabellaTest!F9</f>
         <v>TF003.UC01</v>
       </c>
-      <c r="B48" s="93" t="str">
+      <c r="B48" s="135" t="str">
         <f>TabellaTest!F9</f>
         <v>TF003.UC01</v>
       </c>
-      <c r="C48" s="94"/>
-      <c r="D48" s="94" t="str">
+      <c r="C48" s="136"/>
+      <c r="D48" s="136" t="str">
         <f>TabellaTest!E9</f>
         <v>Ricerca Fine Pena Procedimenti Pendenti</v>
       </c>
-      <c r="E48" s="95"/>
-      <c r="F48" s="94" t="str">
+      <c r="E48" s="122"/>
+      <c r="F48" s="136" t="str">
         <f>TabellaTest!G9</f>
         <v>Verifica: Verificare nel sottosistema SIUS la funzione Ricerca Fine Pena Procedimenti Pendenti per data fine pena reale</v>
       </c>
-      <c r="G48" s="95"/>
+      <c r="G48" s="122"/>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="95"/>
-      <c r="B49" s="156" t="s">
+      <c r="A49" s="122"/>
+      <c r="B49" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="150" t="s">
+      <c r="C49" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="D49" s="151" t="s">
+      <c r="D49" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="E49" s="151" t="s">
+      <c r="E49" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="F49" s="151" t="s">
+      <c r="F49" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="G49" s="151" t="s">
+      <c r="G49" s="88" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="159"/>
-      <c r="B50" s="157" t="s">
+      <c r="A50" s="123"/>
+      <c r="B50" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="152" t="s">
+      <c r="C50" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="153" t="s">
+      <c r="D50" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="153" t="s">
+      <c r="E50" s="90" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="154"/>
-      <c r="G50" s="155"/>
+      <c r="F50" s="91"/>
+      <c r="G50" s="92"/>
     </row>
     <row r="51" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="159"/>
+      <c r="A51" s="123"/>
       <c r="B51" s="60" t="s">
         <v>36</v>
       </c>
@@ -5602,7 +5602,7 @@
       <c r="G51" s="41"/>
     </row>
     <row r="52" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="159"/>
+      <c r="A52" s="123"/>
       <c r="B52" s="61">
         <v>1</v>
       </c>
@@ -5619,8 +5619,8 @@
       <c r="G52" s="41"/>
     </row>
     <row r="53" spans="1:7" s="29" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A53" s="159"/>
-      <c r="B53" s="158" t="s">
+      <c r="A53" s="123"/>
+      <c r="B53" s="95" t="s">
         <v>77</v>
       </c>
       <c r="C53" s="72" t="s">
@@ -5634,7 +5634,7 @@
       <c r="G53" s="41"/>
     </row>
     <row r="54" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="159"/>
+      <c r="A54" s="123"/>
       <c r="B54" s="63">
         <v>2</v>
       </c>
@@ -5651,15 +5651,15 @@
       <c r="G54" s="41"/>
     </row>
     <row r="55" spans="1:7" s="29" customFormat="1" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="98"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="144" t="s">
+      <c r="C55" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D55" s="75" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E55" s="47"/>
       <c r="F55" s="75"/>
@@ -5670,24 +5670,24 @@
         <f>TabellaTest!F10</f>
         <v>TF003.UC02</v>
       </c>
-      <c r="B56" s="96" t="str">
+      <c r="B56" s="128" t="str">
         <f>TabellaTest!F10</f>
         <v>TF003.UC02</v>
       </c>
-      <c r="C56" s="97"/>
-      <c r="D56" s="97" t="str">
+      <c r="C56" s="129"/>
+      <c r="D56" s="129" t="str">
         <f>TabellaTest!E10</f>
         <v>Ricerca Fine Pena Procedimenti Pendenti</v>
       </c>
-      <c r="E56" s="98"/>
-      <c r="F56" s="97" t="str">
+      <c r="E56" s="124"/>
+      <c r="F56" s="129" t="str">
         <f>TabellaTest!G10</f>
         <v>Verifica: Verificare nel sottosistema SIUS la funzione Ricerca Fine Pena Procedimenti Pendenti per fine pena virtuale</v>
       </c>
-      <c r="G56" s="98"/>
+      <c r="G56" s="124"/>
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="95"/>
+      <c r="A57" s="122"/>
       <c r="B57" s="58" t="s">
         <v>31</v>
       </c>
@@ -5708,8 +5708,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="159"/>
-      <c r="B58" s="139" t="s">
+      <c r="A58" s="123"/>
+      <c r="B58" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C58" s="39" t="s">
@@ -5722,13 +5722,13 @@
         <v>148</v>
       </c>
       <c r="F58" s="44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G58" s="41"/>
     </row>
     <row r="59" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="159"/>
-      <c r="B59" s="139" t="s">
+      <c r="A59" s="123"/>
+      <c r="B59" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="39" t="s">
@@ -5742,8 +5742,8 @@
       <c r="G59" s="41"/>
     </row>
     <row r="60" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="159"/>
-      <c r="B60" s="140">
+      <c r="A60" s="123"/>
+      <c r="B60" s="77">
         <v>1</v>
       </c>
       <c r="C60" s="42" t="s">
@@ -5759,8 +5759,8 @@
       <c r="G60" s="41"/>
     </row>
     <row r="61" spans="1:7" s="29" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A61" s="159"/>
-      <c r="B61" s="141" t="s">
+      <c r="A61" s="123"/>
+      <c r="B61" s="78" t="s">
         <v>77</v>
       </c>
       <c r="C61" s="72" t="s">
@@ -5774,15 +5774,15 @@
       <c r="G61" s="41"/>
     </row>
     <row r="62" spans="1:7" s="29" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="159"/>
-      <c r="B62" s="145">
+      <c r="A62" s="123"/>
+      <c r="B62" s="82">
         <v>2</v>
       </c>
       <c r="C62" s="45" t="s">
         <v>40</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E62" s="44"/>
       <c r="F62" s="40" t="s">
@@ -5791,15 +5791,15 @@
       <c r="G62" s="41"/>
     </row>
     <row r="63" spans="1:7" s="29" customFormat="1" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="98"/>
-      <c r="B63" s="143" t="s">
+      <c r="A63" s="124"/>
+      <c r="B63" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="144" t="s">
+      <c r="C63" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D63" s="75" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E63" s="47"/>
       <c r="F63" s="75"/>
@@ -5810,24 +5810,24 @@
         <f>TabellaTest!F11</f>
         <v>TF004.UC01</v>
       </c>
-      <c r="B64" s="92" t="str">
+      <c r="B64" s="130" t="str">
         <f>TabellaTest!C11</f>
         <v>PAR.3.2-048-04</v>
       </c>
-      <c r="C64" s="91"/>
-      <c r="D64" s="91" t="str">
+      <c r="C64" s="131"/>
+      <c r="D64" s="131" t="str">
         <f>TabellaTest!E11</f>
         <v>Condivisione Calcolatrice DL 92/2024 di SIEP lato SIUS</v>
       </c>
-      <c r="E64" s="87"/>
-      <c r="F64" s="91" t="str">
+      <c r="E64" s="132"/>
+      <c r="F64" s="131" t="str">
         <f>TabellaTest!G11</f>
         <v>Condivisione Calcolatrice DL 92/2024 di SIEP lato SIUS</v>
       </c>
-      <c r="G64" s="87"/>
+      <c r="G64" s="132"/>
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="160"/>
+      <c r="A65" s="125"/>
       <c r="B65" s="58" t="s">
         <v>31</v>
       </c>
@@ -5848,8 +5848,8 @@
       </c>
     </row>
     <row r="66" spans="1:7" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="161"/>
-      <c r="B66" s="139" t="s">
+      <c r="A66" s="126"/>
+      <c r="B66" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C66" s="39" t="s">
@@ -5865,32 +5865,32 @@
       <c r="G66" s="41"/>
     </row>
     <row r="67" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="161"/>
-      <c r="B67" s="139" t="s">
+      <c r="A67" s="126"/>
+      <c r="B67" s="76" t="s">
         <v>36</v>
       </c>
       <c r="C67" s="39" t="s">
         <v>38</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E67" s="40"/>
       <c r="F67" s="73" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G67" s="41"/>
     </row>
     <row r="68" spans="1:7" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="161"/>
-      <c r="B68" s="140">
+      <c r="A68" s="126"/>
+      <c r="B68" s="77">
         <v>1</v>
       </c>
       <c r="C68" s="42" t="s">
         <v>39</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E68" s="44"/>
       <c r="F68" s="40" t="s">
@@ -5899,8 +5899,8 @@
       <c r="G68" s="41"/>
     </row>
     <row r="69" spans="1:7" s="29" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A69" s="161"/>
-      <c r="B69" s="142">
+      <c r="A69" s="126"/>
+      <c r="B69" s="79">
         <v>2</v>
       </c>
       <c r="C69" s="45" t="s">
@@ -5911,20 +5911,20 @@
       </c>
       <c r="E69" s="73"/>
       <c r="F69" s="40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G69" s="41"/>
     </row>
     <row r="70" spans="1:7" s="29" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="162"/>
-      <c r="B70" s="143" t="s">
+      <c r="A70" s="127"/>
+      <c r="B70" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C70" s="144" t="s">
+      <c r="C70" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D70" s="75" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E70" s="47"/>
       <c r="F70" s="75"/>
@@ -5937,34 +5937,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="39">
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A57:A63"/>
-    <mergeCell ref="A65:A70"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="A39:A47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="A22:A28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A13:A20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A5:A11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:G1"/>
@@ -5976,6 +5948,34 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A39:A47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="A22:A28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="A57:A63"/>
+    <mergeCell ref="A65:A70"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6503,33 +6503,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="105" t="str">
+      <c r="B1" s="142"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="147" t="str">
         <f>Copertina!B8</f>
         <v>MEV 2026_1 Scheda Intervento Evolutive di SIES v1.0</v>
       </c>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="107"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="149"/>
       <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" s="32" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="108" t="str">
+      <c r="B2" s="145"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="150" t="str">
         <f>Copertina!B4</f>
         <v>B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="110"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="152"/>
       <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7195,65 +7195,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="174" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="113" t="str">
+      <c r="B1" s="174"/>
+      <c r="C1" s="176" t="str">
         <f>Copertina!B8</f>
         <v>MEV 2026_1 Scheda Intervento Evolutive di SIES v1.0</v>
       </c>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
       <c r="F1" s="8"/>
       <c r="G1" s="9"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="112"/>
-      <c r="C2" s="114" t="str">
+      <c r="B2" s="175"/>
+      <c r="C2" s="177" t="str">
         <f>Copertina!B4</f>
         <v>B6437AAAEB-2026-1_Allegato_al_Piano_dei_Test_Evolutive_di_SIES_v1.0.xlsx</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
+      <c r="D2" s="177"/>
+      <c r="E2" s="177"/>
       <c r="F2" s="10"/>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:9" s="12" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="125"/>
-      <c r="G3" s="126" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="160"/>
+      <c r="G3" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="127"/>
-      <c r="I3" s="128"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="163"/>
     </row>
     <row r="4" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="135" t="s">
+      <c r="A4" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="138"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="131"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="173"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="166"/>
     </row>
     <row r="5" spans="1:9" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="119"/>
+      <c r="A5" s="154"/>
       <c r="B5" s="14">
         <v>1</v>
       </c>
@@ -7266,9 +7266,9 @@
       <c r="E5" s="15">
         <v>4</v>
       </c>
-      <c r="G5" s="129"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="131"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="166"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
@@ -7290,9 +7290,9 @@
         <f>COUNTIFS(TabellaTest!$H$6:$H$306,4,TabellaTest!$I$6:$I$306,"A",TabellaTest!$J$6:$J$306,"KO")</f>
         <v>0</v>
       </c>
-      <c r="G6" s="129"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="131"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="166"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
@@ -7314,9 +7314,9 @@
         <f>COUNTIFS(TabellaTest!$H$6:$H$306,4,TabellaTest!$I$6:$I$306,"B",TabellaTest!$J$6:$J$306,"KO")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="131"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="166"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
@@ -7338,9 +7338,9 @@
         <f>COUNTIFS(TabellaTest!$H$6:$H$306,4,TabellaTest!$I$6:$I$306,"C",TabellaTest!$J$6:$J$306,"KO")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="132"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="134"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="168"/>
+      <c r="I8" s="169"/>
     </row>
     <row r="9" spans="1:9" ht="13.9" x14ac:dyDescent="0.3">
       <c r="G9" s="20"/>
@@ -7350,27 +7350,27 @@
     <row r="12" spans="1:9" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:9" ht="14.45" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:9" s="12" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="178" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="117"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="179"/>
+      <c r="D14" s="179"/>
+      <c r="E14" s="180"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="118" t="s">
+      <c r="A15" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="120" t="s">
+      <c r="B15" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="122"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="157"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="119"/>
+      <c r="A16" s="154"/>
       <c r="B16" s="21">
         <v>1</v>
       </c>
@@ -7450,17 +7450,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="yK4t762dsqdaSNJbIJdXYOJ9V6yhJPk90M8BFw4lbAyBYOqkLwUcsAp6Hzt1n+PAyjFA1QcVZEWzBN39IMR6Og==" saltValue="SATjaK3ZpVyROTc4J1W+8Q==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="G3:I8"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:E8">
     <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
@@ -7486,6 +7486,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E8661A27DDB5564DB260D886781D2EAA" ma:contentTypeVersion="11" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="18792330a02ec04c91ad73c241055c66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75e085f0-8718-4866-8354-8788ce640d21" xmlns:ns3="f725a5e7-e092-40ab-9dcc-515fa0d4e97d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d7bf31fac48d061536d5445345bac2c5" ns2:_="" ns3:_="">
     <xsd:import namespace="75e085f0-8718-4866-8354-8788ce640d21"/>
@@ -7674,15 +7683,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7695,6 +7695,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C65E7D-62B2-458A-867B-AE3870757B77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5455A0B3-A4AD-4E08-9E6A-60A20509E259}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7713,14 +7721,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C65E7D-62B2-458A-867B-AE3870757B77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{814AF41E-29B3-43BC-B98B-31320DADB270}">
   <ds:schemaRefs>
